--- a/VerveStacks_ITA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B4BC50-1BB2-4A02-A5FB-566E3EEF9420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AA4B7B-FB25-4791-BC4D-5053CE24B8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6895,7 +6895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2991928-2825-407E-8BAC-3878D2697FBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED86C76-1D62-4585-83FA-D3CD4CE78456}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0318C6-B5E5-4E93-9EDD-18D2DA2DC2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9017D96-4B14-4059-83F2-66EFDF4A3204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5087,7 +5087,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4B2C03-7D9E-408D-86C8-13957D6EE8A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCDB881-08C7-4B26-AB10-1B088D8B8D58}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9017D96-4B14-4059-83F2-66EFDF4A3204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61859A1F-11D4-4A18-A5A4-F566A04D535C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5087,7 +5087,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCDB881-08C7-4B26-AB10-1B088D8B8D58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64DC0FF5-D73B-4D79-B859-2EAB7B686A3B}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
